--- a/full schema for dbo FitTracker.xlsx
+++ b/full schema for dbo FitTracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Sites\ajsm-gym\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468D64E2-0D4F-4115-8C55-F9FB24CA3F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9A667F-9AAA-4B0F-91D5-CE2A0371BF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D96D6B20-332E-44C8-8305-B4C024F7D8BC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="225">
   <si>
     <t>TableName</t>
   </si>
@@ -757,7 +757,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -768,6 +768,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00BBCA"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -839,7 +845,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -855,6 +861,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1622,7 +1631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0988D80-A527-4519-B2FE-118A4D25C0D9}">
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:L148"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -1635,10 +1644,12 @@
     <col min="8" max="8" width="9.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="2"/>
+    <col min="11" max="11" width="8.88671875" style="2"/>
+    <col min="12" max="12" width="20.21875" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1670,7 +1681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>140</v>
       </c>
@@ -1699,8 +1710,11 @@
         <v>0</v>
       </c>
       <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L2" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>140</v>
       </c>
@@ -1729,8 +1743,11 @@
         <v>0</v>
       </c>
       <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L3" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>140</v>
       </c>
@@ -1759,8 +1776,11 @@
         <v>0</v>
       </c>
       <c r="J4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L4" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>140</v>
       </c>
@@ -1789,8 +1809,11 @@
         <v>1</v>
       </c>
       <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L5" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>95</v>
       </c>
@@ -1819,8 +1842,11 @@
         <v>0</v>
       </c>
       <c r="J6" s="4"/>
-    </row>
-    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>95</v>
       </c>
@@ -1849,8 +1875,11 @@
         <v>0</v>
       </c>
       <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L7" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>95</v>
       </c>
@@ -1881,8 +1910,11 @@
       <c r="J8" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L8" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>95</v>
       </c>
@@ -1913,8 +1945,11 @@
       <c r="J9" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L9" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>95</v>
       </c>
@@ -1943,8 +1978,11 @@
         <v>1</v>
       </c>
       <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L10" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>95</v>
       </c>
@@ -1973,8 +2011,11 @@
         <v>0</v>
       </c>
       <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L11" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>95</v>
       </c>
@@ -2003,8 +2044,11 @@
         <v>0</v>
       </c>
       <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L12" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>95</v>
       </c>
@@ -2033,8 +2077,11 @@
         <v>0</v>
       </c>
       <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L13" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>95</v>
       </c>
@@ -2063,8 +2110,11 @@
         <v>0</v>
       </c>
       <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L14" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>95</v>
       </c>
@@ -2095,8 +2145,11 @@
       <c r="J15" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L15" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>151</v>
       </c>
@@ -2125,8 +2178,11 @@
         <v>1</v>
       </c>
       <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L16" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>151</v>
       </c>
@@ -2155,8 +2211,11 @@
         <v>0</v>
       </c>
       <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L17" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>151</v>
       </c>
@@ -2185,8 +2244,11 @@
         <v>0</v>
       </c>
       <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L18" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>154</v>
       </c>
@@ -2215,8 +2277,11 @@
         <v>0</v>
       </c>
       <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L19" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>154</v>
       </c>
@@ -2245,8 +2310,11 @@
         <v>1</v>
       </c>
       <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L20" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>10</v>
       </c>
@@ -2275,8 +2343,11 @@
         <v>0</v>
       </c>
       <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L21" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>10</v>
       </c>
@@ -2305,8 +2376,11 @@
         <v>0</v>
       </c>
       <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L22" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>10</v>
       </c>
@@ -2335,8 +2409,9 @@
         <v>1</v>
       </c>
       <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L23"/>
+    </row>
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>87</v>
       </c>
@@ -2365,8 +2440,9 @@
         <v>0</v>
       </c>
       <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L24"/>
+    </row>
+    <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>87</v>
       </c>
@@ -2395,8 +2471,9 @@
         <v>0</v>
       </c>
       <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L25"/>
+    </row>
+    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>87</v>
       </c>
@@ -2427,8 +2504,9 @@
       <c r="J26" s="4" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L26"/>
+    </row>
+    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>87</v>
       </c>
@@ -2457,8 +2535,9 @@
         <v>0</v>
       </c>
       <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L27"/>
+    </row>
+    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>87</v>
       </c>
@@ -2487,8 +2566,9 @@
         <v>0</v>
       </c>
       <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L28"/>
+    </row>
+    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>87</v>
       </c>
@@ -2517,8 +2597,9 @@
         <v>1</v>
       </c>
       <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L29"/>
+    </row>
+    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>87</v>
       </c>
@@ -2549,8 +2630,9 @@
       <c r="J30" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L30"/>
+    </row>
+    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>16</v>
       </c>
@@ -2581,8 +2663,9 @@
       <c r="J31" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L31"/>
+    </row>
+    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>16</v>
       </c>
@@ -2611,8 +2694,9 @@
         <v>1</v>
       </c>
       <c r="J32" s="4"/>
-    </row>
-    <row r="33" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L32"/>
+    </row>
+    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>16</v>
       </c>
@@ -2641,8 +2725,9 @@
         <v>0</v>
       </c>
       <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L33"/>
+    </row>
+    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>16</v>
       </c>
@@ -2671,8 +2756,9 @@
         <v>0</v>
       </c>
       <c r="J34" s="4"/>
-    </row>
-    <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L34"/>
+    </row>
+    <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>16</v>
       </c>
@@ -2701,8 +2787,9 @@
         <v>0</v>
       </c>
       <c r="J35" s="4"/>
-    </row>
-    <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L35"/>
+    </row>
+    <row r="36" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>16</v>
       </c>
@@ -2731,8 +2818,9 @@
         <v>0</v>
       </c>
       <c r="J36" s="4"/>
-    </row>
-    <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L36"/>
+    </row>
+    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>24</v>
       </c>
@@ -2761,8 +2849,9 @@
         <v>0</v>
       </c>
       <c r="J37" s="4"/>
-    </row>
-    <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L37"/>
+    </row>
+    <row r="38" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>24</v>
       </c>
@@ -2791,8 +2880,9 @@
         <v>0</v>
       </c>
       <c r="J38" s="4"/>
-    </row>
-    <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L38"/>
+    </row>
+    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>24</v>
       </c>
@@ -2821,8 +2911,9 @@
         <v>0</v>
       </c>
       <c r="J39" s="4"/>
-    </row>
-    <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L39"/>
+    </row>
+    <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>24</v>
       </c>
@@ -2851,8 +2942,9 @@
         <v>0</v>
       </c>
       <c r="J40" s="4"/>
-    </row>
-    <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L40"/>
+    </row>
+    <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>24</v>
       </c>
@@ -2881,8 +2973,9 @@
         <v>1</v>
       </c>
       <c r="J41" s="4"/>
-    </row>
-    <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L41"/>
+    </row>
+    <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>24</v>
       </c>
@@ -2911,8 +3004,9 @@
         <v>0</v>
       </c>
       <c r="J42" s="4"/>
-    </row>
-    <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L42"/>
+    </row>
+    <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>105</v>
       </c>
@@ -2941,8 +3035,9 @@
         <v>0</v>
       </c>
       <c r="J43" s="4"/>
-    </row>
-    <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L43"/>
+    </row>
+    <row r="44" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>105</v>
       </c>
@@ -2971,8 +3066,9 @@
         <v>0</v>
       </c>
       <c r="J44" s="4"/>
-    </row>
-    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L44"/>
+    </row>
+    <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>105</v>
       </c>
@@ -3001,8 +3097,9 @@
         <v>0</v>
       </c>
       <c r="J45" s="4"/>
-    </row>
-    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L45"/>
+    </row>
+    <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>105</v>
       </c>
@@ -3033,8 +3130,9 @@
       <c r="J46" s="4" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L46"/>
+    </row>
+    <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>105</v>
       </c>
@@ -3065,8 +3163,9 @@
       <c r="J47" s="4" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L47"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>105</v>
       </c>
@@ -3095,8 +3194,9 @@
         <v>0</v>
       </c>
       <c r="J48" s="4"/>
-    </row>
-    <row r="49" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L48"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>105</v>
       </c>
@@ -3125,8 +3225,9 @@
         <v>1</v>
       </c>
       <c r="J49" s="4"/>
-    </row>
-    <row r="50" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L49"/>
+    </row>
+    <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>105</v>
       </c>
@@ -3155,8 +3256,9 @@
         <v>0</v>
       </c>
       <c r="J50" s="4"/>
-    </row>
-    <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L50"/>
+    </row>
+    <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>105</v>
       </c>
@@ -3185,8 +3287,9 @@
         <v>0</v>
       </c>
       <c r="J51" s="4"/>
-    </row>
-    <row r="52" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L51"/>
+    </row>
+    <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>105</v>
       </c>
@@ -3215,8 +3318,9 @@
         <v>0</v>
       </c>
       <c r="J52" s="4"/>
-    </row>
-    <row r="53" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L52"/>
+    </row>
+    <row r="53" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>108</v>
       </c>
@@ -3245,8 +3349,9 @@
         <v>0</v>
       </c>
       <c r="J53" s="4"/>
-    </row>
-    <row r="54" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L53"/>
+    </row>
+    <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>108</v>
       </c>
@@ -3275,8 +3380,9 @@
         <v>0</v>
       </c>
       <c r="J54" s="4"/>
-    </row>
-    <row r="55" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L54"/>
+    </row>
+    <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>108</v>
       </c>
@@ -3305,8 +3411,9 @@
         <v>0</v>
       </c>
       <c r="J55" s="4"/>
-    </row>
-    <row r="56" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L55"/>
+    </row>
+    <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>108</v>
       </c>
@@ -3335,8 +3442,9 @@
         <v>0</v>
       </c>
       <c r="J56" s="4"/>
-    </row>
-    <row r="57" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L56"/>
+    </row>
+    <row r="57" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>108</v>
       </c>
@@ -3367,8 +3475,9 @@
       <c r="J57" s="4" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L57"/>
+    </row>
+    <row r="58" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>108</v>
       </c>
@@ -3399,8 +3508,9 @@
       <c r="J58" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L58"/>
+    </row>
+    <row r="59" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>108</v>
       </c>
@@ -3431,8 +3541,9 @@
       <c r="J59" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L59"/>
+    </row>
+    <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>108</v>
       </c>
@@ -3463,8 +3574,9 @@
       <c r="J60" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L60"/>
+    </row>
+    <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>108</v>
       </c>
@@ -3493,8 +3605,9 @@
         <v>0</v>
       </c>
       <c r="J61" s="4"/>
-    </row>
-    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L61"/>
+    </row>
+    <row r="62" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>108</v>
       </c>
@@ -3523,8 +3636,9 @@
         <v>0</v>
       </c>
       <c r="J62" s="4"/>
-    </row>
-    <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L62"/>
+    </row>
+    <row r="63" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>108</v>
       </c>
@@ -3553,8 +3667,9 @@
         <v>0</v>
       </c>
       <c r="J63" s="4"/>
-    </row>
-    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L63"/>
+    </row>
+    <row r="64" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>108</v>
       </c>
@@ -3585,8 +3700,9 @@
       <c r="J64" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L64"/>
+    </row>
+    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>108</v>
       </c>
@@ -3617,8 +3733,9 @@
       <c r="J65" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L65"/>
+    </row>
+    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>108</v>
       </c>
@@ -3649,8 +3766,9 @@
       <c r="J66" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L66"/>
+    </row>
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>108</v>
       </c>
@@ -3681,8 +3799,9 @@
       <c r="J67" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L67"/>
+    </row>
+    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>108</v>
       </c>
@@ -3713,8 +3832,9 @@
       <c r="J68" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L68"/>
+    </row>
+    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>180</v>
       </c>
@@ -3743,8 +3863,9 @@
         <v>1</v>
       </c>
       <c r="J69" s="4"/>
-    </row>
-    <row r="70" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L69"/>
+    </row>
+    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>180</v>
       </c>
@@ -3773,8 +3894,9 @@
         <v>0</v>
       </c>
       <c r="J70" s="4"/>
-    </row>
-    <row r="71" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L70"/>
+    </row>
+    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>180</v>
       </c>
@@ -3803,8 +3925,9 @@
         <v>0</v>
       </c>
       <c r="J71" s="4"/>
-    </row>
-    <row r="72" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L71"/>
+    </row>
+    <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>180</v>
       </c>
@@ -3833,8 +3956,9 @@
         <v>0</v>
       </c>
       <c r="J72" s="4"/>
-    </row>
-    <row r="73" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L72"/>
+    </row>
+    <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>180</v>
       </c>
@@ -3863,8 +3987,9 @@
         <v>0</v>
       </c>
       <c r="J73" s="4"/>
-    </row>
-    <row r="74" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L73"/>
+    </row>
+    <row r="74" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>180</v>
       </c>
@@ -3893,8 +4018,9 @@
         <v>0</v>
       </c>
       <c r="J74" s="4"/>
-    </row>
-    <row r="75" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L74"/>
+    </row>
+    <row r="75" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>30</v>
       </c>
@@ -3923,8 +4049,9 @@
         <v>0</v>
       </c>
       <c r="J75" s="4"/>
-    </row>
-    <row r="76" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L75"/>
+    </row>
+    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>30</v>
       </c>
@@ -3953,8 +4080,9 @@
         <v>0</v>
       </c>
       <c r="J76" s="4"/>
-    </row>
-    <row r="77" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L76"/>
+    </row>
+    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>30</v>
       </c>
@@ -3985,8 +4113,9 @@
       <c r="J77" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L77"/>
+    </row>
+    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>30</v>
       </c>
@@ -4017,8 +4146,9 @@
       <c r="J78" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L78"/>
+    </row>
+    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>30</v>
       </c>
@@ -4049,8 +4179,9 @@
       <c r="J79" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L79"/>
+    </row>
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>30</v>
       </c>
@@ -4079,8 +4210,9 @@
         <v>1</v>
       </c>
       <c r="J80" s="4"/>
-    </row>
-    <row r="81" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L80"/>
+    </row>
+    <row r="81" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>30</v>
       </c>
@@ -4111,8 +4243,9 @@
       <c r="J81" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L81"/>
+    </row>
+    <row r="82" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>122</v>
       </c>
@@ -4141,8 +4274,9 @@
         <v>0</v>
       </c>
       <c r="J82" s="4"/>
-    </row>
-    <row r="83" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L82"/>
+    </row>
+    <row r="83" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>122</v>
       </c>
@@ -4171,8 +4305,9 @@
         <v>0</v>
       </c>
       <c r="J83" s="4"/>
-    </row>
-    <row r="84" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L83"/>
+    </row>
+    <row r="84" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>122</v>
       </c>
@@ -4201,8 +4336,9 @@
         <v>0</v>
       </c>
       <c r="J84" s="4"/>
-    </row>
-    <row r="85" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L84"/>
+    </row>
+    <row r="85" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>122</v>
       </c>
@@ -4231,8 +4367,9 @@
         <v>1</v>
       </c>
       <c r="J85" s="4"/>
-    </row>
-    <row r="86" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L85"/>
+    </row>
+    <row r="86" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>122</v>
       </c>
@@ -4261,8 +4398,9 @@
         <v>0</v>
       </c>
       <c r="J86" s="4"/>
-    </row>
-    <row r="87" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L86"/>
+    </row>
+    <row r="87" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>122</v>
       </c>
@@ -4293,8 +4431,9 @@
       <c r="J87" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L87"/>
+    </row>
+    <row r="88" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>124</v>
       </c>
@@ -4323,8 +4462,9 @@
         <v>0</v>
       </c>
       <c r="J88" s="4"/>
-    </row>
-    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L88"/>
+    </row>
+    <row r="89" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>124</v>
       </c>
@@ -4355,8 +4495,9 @@
       <c r="J89" s="4" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L89"/>
+    </row>
+    <row r="90" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>124</v>
       </c>
@@ -4385,8 +4526,9 @@
         <v>1</v>
       </c>
       <c r="J90" s="4"/>
-    </row>
-    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L90"/>
+    </row>
+    <row r="91" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>124</v>
       </c>
@@ -4415,8 +4557,9 @@
         <v>0</v>
       </c>
       <c r="J91" s="4"/>
-    </row>
-    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L91"/>
+    </row>
+    <row r="92" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>124</v>
       </c>
@@ -4445,8 +4588,9 @@
         <v>0</v>
       </c>
       <c r="J92" s="4"/>
-    </row>
-    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L92"/>
+    </row>
+    <row r="93" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>43</v>
       </c>
@@ -4475,8 +4619,9 @@
         <v>0</v>
       </c>
       <c r="J93" s="4"/>
-    </row>
-    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L93"/>
+    </row>
+    <row r="94" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4650,9 @@
         <v>0</v>
       </c>
       <c r="J94" s="4"/>
-    </row>
-    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L94"/>
+    </row>
+    <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>43</v>
       </c>
@@ -4535,8 +4681,9 @@
         <v>0</v>
       </c>
       <c r="J95" s="4"/>
-    </row>
-    <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L95"/>
+    </row>
+    <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>43</v>
       </c>
@@ -4567,8 +4714,9 @@
       <c r="J96" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L96"/>
+    </row>
+    <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>43</v>
       </c>
@@ -4599,8 +4747,9 @@
       <c r="J97" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L97"/>
+    </row>
+    <row r="98" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>43</v>
       </c>
@@ -4629,8 +4778,9 @@
         <v>0</v>
       </c>
       <c r="J98" s="4"/>
-    </row>
-    <row r="99" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L98"/>
+    </row>
+    <row r="99" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>43</v>
       </c>
@@ -4659,8 +4809,9 @@
         <v>0</v>
       </c>
       <c r="J99" s="4"/>
-    </row>
-    <row r="100" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L99"/>
+    </row>
+    <row r="100" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>43</v>
       </c>
@@ -4689,8 +4840,9 @@
         <v>0</v>
       </c>
       <c r="J100" s="4"/>
-    </row>
-    <row r="101" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L100"/>
+    </row>
+    <row r="101" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>43</v>
       </c>
@@ -4721,8 +4873,9 @@
       <c r="J101" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L101"/>
+    </row>
+    <row r="102" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>50</v>
       </c>
@@ -4751,8 +4904,9 @@
         <v>0</v>
       </c>
       <c r="J102" s="4"/>
-    </row>
-    <row r="103" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L102"/>
+    </row>
+    <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>50</v>
       </c>
@@ -4781,8 +4935,9 @@
         <v>0</v>
       </c>
       <c r="J103" s="4"/>
-    </row>
-    <row r="104" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L103"/>
+    </row>
+    <row r="104" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>50</v>
       </c>
@@ -4811,8 +4966,9 @@
         <v>0</v>
       </c>
       <c r="J104" s="4"/>
-    </row>
-    <row r="105" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L104"/>
+    </row>
+    <row r="105" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>50</v>
       </c>
@@ -4841,8 +4997,9 @@
         <v>0</v>
       </c>
       <c r="J105" s="4"/>
-    </row>
-    <row r="106" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L105"/>
+    </row>
+    <row r="106" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>50</v>
       </c>
@@ -4871,8 +5028,9 @@
         <v>0</v>
       </c>
       <c r="J106" s="4"/>
-    </row>
-    <row r="107" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L106"/>
+    </row>
+    <row r="107" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>50</v>
       </c>
@@ -4901,8 +5059,9 @@
         <v>0</v>
       </c>
       <c r="J107" s="4"/>
-    </row>
-    <row r="108" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L107"/>
+    </row>
+    <row r="108" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>50</v>
       </c>
@@ -4931,8 +5090,9 @@
         <v>0</v>
       </c>
       <c r="J108" s="4"/>
-    </row>
-    <row r="109" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L108"/>
+    </row>
+    <row r="109" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>50</v>
       </c>
@@ -4961,8 +5121,9 @@
         <v>0</v>
       </c>
       <c r="J109" s="4"/>
-    </row>
-    <row r="110" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L109"/>
+    </row>
+    <row r="110" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>50</v>
       </c>
@@ -4991,8 +5152,9 @@
         <v>0</v>
       </c>
       <c r="J110" s="4"/>
-    </row>
-    <row r="111" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L110"/>
+    </row>
+    <row r="111" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>50</v>
       </c>
@@ -5021,8 +5183,9 @@
         <v>0</v>
       </c>
       <c r="J111" s="4"/>
-    </row>
-    <row r="112" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L111"/>
+    </row>
+    <row r="112" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>50</v>
       </c>
@@ -5051,8 +5214,9 @@
         <v>0</v>
       </c>
       <c r="J112" s="4"/>
-    </row>
-    <row r="113" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L112"/>
+    </row>
+    <row r="113" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>50</v>
       </c>
@@ -5081,8 +5245,9 @@
         <v>0</v>
       </c>
       <c r="J113" s="4"/>
-    </row>
-    <row r="114" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L113"/>
+    </row>
+    <row r="114" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>50</v>
       </c>
@@ -5113,8 +5278,9 @@
       <c r="J114" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L114"/>
+    </row>
+    <row r="115" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>50</v>
       </c>
@@ -5145,8 +5311,9 @@
       <c r="J115" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L115"/>
+    </row>
+    <row r="116" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>50</v>
       </c>
@@ -5177,8 +5344,9 @@
       <c r="J116" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L116"/>
+    </row>
+    <row r="117" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>50</v>
       </c>
@@ -5209,8 +5377,9 @@
       <c r="J117" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L117"/>
+    </row>
+    <row r="118" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>50</v>
       </c>
@@ -5239,8 +5408,9 @@
         <v>1</v>
       </c>
       <c r="J118" s="4"/>
-    </row>
-    <row r="119" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L118"/>
+    </row>
+    <row r="119" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>50</v>
       </c>
@@ -5269,8 +5439,9 @@
         <v>0</v>
       </c>
       <c r="J119" s="4"/>
-    </row>
-    <row r="120" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L119"/>
+    </row>
+    <row r="120" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>50</v>
       </c>
@@ -5299,8 +5470,9 @@
         <v>0</v>
       </c>
       <c r="J120" s="4"/>
-    </row>
-    <row r="121" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L120"/>
+    </row>
+    <row r="121" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>50</v>
       </c>
@@ -5329,8 +5501,9 @@
         <v>0</v>
       </c>
       <c r="J121" s="4"/>
-    </row>
-    <row r="122" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L121"/>
+    </row>
+    <row r="122" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>191</v>
       </c>
@@ -5359,8 +5532,9 @@
         <v>1</v>
       </c>
       <c r="J122" s="4"/>
-    </row>
-    <row r="123" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L122"/>
+    </row>
+    <row r="123" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>191</v>
       </c>
@@ -5389,8 +5563,9 @@
         <v>0</v>
       </c>
       <c r="J123" s="4"/>
-    </row>
-    <row r="124" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L123"/>
+    </row>
+    <row r="124" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>191</v>
       </c>
@@ -5419,8 +5594,9 @@
         <v>0</v>
       </c>
       <c r="J124" s="4"/>
-    </row>
-    <row r="125" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L124"/>
+    </row>
+    <row r="125" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>134</v>
       </c>
@@ -5451,8 +5627,9 @@
       <c r="J125" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L125"/>
+    </row>
+    <row r="126" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>134</v>
       </c>
@@ -5481,8 +5658,9 @@
         <v>0</v>
       </c>
       <c r="J126" s="4"/>
-    </row>
-    <row r="127" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L126"/>
+    </row>
+    <row r="127" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>134</v>
       </c>
@@ -5511,8 +5689,9 @@
         <v>0</v>
       </c>
       <c r="J127" s="4"/>
-    </row>
-    <row r="128" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L127"/>
+    </row>
+    <row r="128" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
         <v>134</v>
       </c>
@@ -5541,8 +5720,9 @@
         <v>1</v>
       </c>
       <c r="J128" s="4"/>
-    </row>
-    <row r="129" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L128"/>
+    </row>
+    <row r="129" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>134</v>
       </c>
@@ -5571,8 +5751,9 @@
         <v>0</v>
       </c>
       <c r="J129" s="4"/>
-    </row>
-    <row r="130" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L129"/>
+    </row>
+    <row r="130" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
         <v>136</v>
       </c>
@@ -5601,8 +5782,9 @@
         <v>0</v>
       </c>
       <c r="J130" s="4"/>
-    </row>
-    <row r="131" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L130"/>
+    </row>
+    <row r="131" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>136</v>
       </c>
@@ -5631,8 +5813,9 @@
         <v>0</v>
       </c>
       <c r="J131" s="4"/>
-    </row>
-    <row r="132" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L131"/>
+    </row>
+    <row r="132" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
         <v>136</v>
       </c>
@@ -5661,8 +5844,9 @@
         <v>0</v>
       </c>
       <c r="J132" s="4"/>
-    </row>
-    <row r="133" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L132"/>
+    </row>
+    <row r="133" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
         <v>136</v>
       </c>
@@ -5693,8 +5877,9 @@
       <c r="J133" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L133"/>
+    </row>
+    <row r="134" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>136</v>
       </c>
@@ -5723,8 +5908,9 @@
         <v>0</v>
       </c>
       <c r="J134" s="4"/>
-    </row>
-    <row r="135" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L134"/>
+    </row>
+    <row r="135" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>136</v>
       </c>
@@ -5753,8 +5939,9 @@
         <v>0</v>
       </c>
       <c r="J135" s="4"/>
-    </row>
-    <row r="136" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L135"/>
+    </row>
+    <row r="136" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>136</v>
       </c>
@@ -5783,8 +5970,9 @@
         <v>1</v>
       </c>
       <c r="J136" s="4"/>
-    </row>
-    <row r="137" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L136"/>
+    </row>
+    <row r="137" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>136</v>
       </c>
@@ -5813,8 +6001,9 @@
         <v>0</v>
       </c>
       <c r="J137" s="4"/>
-    </row>
-    <row r="138" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L137"/>
+    </row>
+    <row r="138" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>136</v>
       </c>
@@ -5843,8 +6032,9 @@
         <v>0</v>
       </c>
       <c r="J138" s="4"/>
-    </row>
-    <row r="139" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L138"/>
+    </row>
+    <row r="139" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>138</v>
       </c>
@@ -5875,8 +6065,9 @@
       <c r="J139" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="140" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L139"/>
+    </row>
+    <row r="140" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>138</v>
       </c>
@@ -5905,8 +6096,9 @@
         <v>0</v>
       </c>
       <c r="J140" s="4"/>
-    </row>
-    <row r="141" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L140"/>
+    </row>
+    <row r="141" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>138</v>
       </c>
@@ -5935,8 +6127,9 @@
         <v>1</v>
       </c>
       <c r="J141" s="4"/>
-    </row>
-    <row r="142" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L141"/>
+    </row>
+    <row r="142" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>138</v>
       </c>
@@ -5965,8 +6158,9 @@
         <v>0</v>
       </c>
       <c r="J142" s="4"/>
-    </row>
-    <row r="143" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L142"/>
+    </row>
+    <row r="143" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>194</v>
       </c>
@@ -5995,8 +6189,9 @@
         <v>0</v>
       </c>
       <c r="J143" s="4"/>
-    </row>
-    <row r="144" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L143"/>
+    </row>
+    <row r="144" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>194</v>
       </c>
@@ -6025,8 +6220,9 @@
         <v>0</v>
       </c>
       <c r="J144" s="4"/>
-    </row>
-    <row r="145" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L144"/>
+    </row>
+    <row r="145" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>194</v>
       </c>
@@ -6055,8 +6251,9 @@
         <v>0</v>
       </c>
       <c r="J145" s="4"/>
-    </row>
-    <row r="146" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L145"/>
+    </row>
+    <row r="146" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>194</v>
       </c>
@@ -6085,8 +6282,9 @@
         <v>0</v>
       </c>
       <c r="J146" s="4"/>
-    </row>
-    <row r="147" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L146"/>
+    </row>
+    <row r="147" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>194</v>
       </c>
@@ -6115,8 +6313,9 @@
         <v>0</v>
       </c>
       <c r="J147" s="4"/>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="L147"/>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
         <v>194</v>
       </c>
@@ -6145,6 +6344,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="6"/>
+      <c r="L148"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/full schema for dbo FitTracker.xlsx
+++ b/full schema for dbo FitTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Sites\ajsm-gym\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9A667F-9AAA-4B0F-91D5-CE2A0371BF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE93733C-B069-4B43-8E33-5D7DB44E4055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D96D6B20-332E-44C8-8305-B4C024F7D8BC}"/>
+    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="12216" activeTab="1" xr2:uid="{D96D6B20-332E-44C8-8305-B4C024F7D8BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="224">
   <si>
     <t>TableName</t>
   </si>
@@ -188,9 +188,6 @@
   </si>
   <si>
     <t>date</t>
-  </si>
-  <si>
-    <t>IsFirstLogin</t>
   </si>
   <si>
     <t>TestRecords</t>
@@ -1313,10 +1310,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F4A3D023-C026-4B77-B0FC-F08661E4D33F}" name="Table3" displayName="Table3" ref="A1:J148" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
-  <autoFilter ref="A1:J148" xr:uid="{F4A3D023-C026-4B77-B0FC-F08661E4D33F}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J148">
-    <sortCondition ref="A1:A148"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F4A3D023-C026-4B77-B0FC-F08661E4D33F}" name="Table3" displayName="Table3" ref="A1:J141" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+  <autoFilter ref="A1:J141" xr:uid="{F4A3D023-C026-4B77-B0FC-F08661E4D33F}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J141">
+    <sortCondition ref="A1:A141"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{992C5941-FBF6-4898-BA90-142FE637572B}" name="TableName" dataDxfId="9"/>
@@ -1631,7 +1628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0988D80-A527-4519-B2FE-118A4D25C0D9}">
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -1683,7 +1680,7 @@
     </row>
     <row r="2" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B2" s="4">
         <v>3</v>
@@ -1711,18 +1708,18 @@
       </c>
       <c r="J2" s="4"/>
       <c r="L2" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B3" s="4">
         <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>14</v>
@@ -1744,18 +1741,18 @@
       </c>
       <c r="J3" s="4"/>
       <c r="L3" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B4" s="4">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>14</v>
@@ -1777,18 +1774,18 @@
       </c>
       <c r="J4" s="4"/>
       <c r="L4" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
@@ -1810,18 +1807,18 @@
       </c>
       <c r="J5" s="4"/>
       <c r="L5" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="4">
         <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>22</v>
@@ -1848,13 +1845,13 @@
     </row>
     <row r="7" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7" s="4">
         <v>10</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>22</v>
@@ -1876,12 +1873,12 @@
       </c>
       <c r="J7" s="4"/>
       <c r="L7" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B8" s="4">
         <v>7</v>
@@ -1916,7 +1913,7 @@
     </row>
     <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9" s="4">
         <v>8</v>
@@ -1951,13 +1948,13 @@
     </row>
     <row r="10" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>12</v>
@@ -1979,12 +1976,12 @@
       </c>
       <c r="J10" s="4"/>
       <c r="L10" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B11" s="4">
         <v>2</v>
@@ -2012,18 +2009,18 @@
       </c>
       <c r="J11" s="4"/>
       <c r="L11" s="4" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B12" s="4">
         <v>3</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>12</v>
@@ -2045,18 +2042,18 @@
       </c>
       <c r="J12" s="4"/>
       <c r="L12" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4">
         <v>11</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>12</v>
@@ -2083,13 +2080,13 @@
     </row>
     <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B14" s="4">
         <v>5</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>41</v>
@@ -2111,18 +2108,18 @@
       </c>
       <c r="J14" s="4"/>
       <c r="L14" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15" s="4">
         <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>41</v>
@@ -2143,21 +2140,21 @@
         <v>0</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>12</v>
@@ -2184,13 +2181,13 @@
     </row>
     <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="4">
         <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>48</v>
@@ -2212,18 +2209,18 @@
       </c>
       <c r="J17" s="4"/>
       <c r="L17" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B18" s="4">
         <v>3</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>48</v>
@@ -2245,12 +2242,12 @@
       </c>
       <c r="J18" s="4"/>
       <c r="L18" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B19" s="4">
         <v>2</v>
@@ -2278,18 +2275,18 @@
       </c>
       <c r="J19" s="4"/>
       <c r="L19" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="B20" s="4">
-        <v>1</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>12</v>
@@ -2311,7 +2308,7 @@
       </c>
       <c r="J20" s="4"/>
       <c r="L20" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2344,7 +2341,7 @@
       </c>
       <c r="J21" s="4"/>
       <c r="L21" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2377,7 +2374,7 @@
       </c>
       <c r="J22" s="4"/>
       <c r="L22" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2413,13 +2410,13 @@
     </row>
     <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" s="4">
         <v>2</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>14</v>
@@ -2444,13 +2441,13 @@
     </row>
     <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B25" s="4">
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>32</v>
@@ -2475,13 +2472,13 @@
     </row>
     <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B26" s="4">
         <v>6</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>22</v>
@@ -2502,13 +2499,13 @@
         <v>0</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L26"/>
     </row>
     <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B27" s="4">
         <v>3</v>
@@ -2539,7 +2536,7 @@
     </row>
     <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" s="4">
         <v>4</v>
@@ -2570,13 +2567,13 @@
     </row>
     <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B29" s="4">
         <v>1</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>12</v>
@@ -2601,13 +2598,13 @@
     </row>
     <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B30" s="4">
         <v>5</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>41</v>
@@ -2628,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L30"/>
     </row>
@@ -2803,7 +2800,7 @@
         <v>14</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F36" s="4">
         <v>0</v>
@@ -3008,13 +3005,13 @@
     </row>
     <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B43" s="4">
         <v>5</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>14</v>
@@ -3039,13 +3036,13 @@
     </row>
     <row r="44" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B44" s="4">
         <v>10</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>14</v>
@@ -3070,13 +3067,13 @@
     </row>
     <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B45" s="4">
         <v>8</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>32</v>
@@ -3101,13 +3098,13 @@
     </row>
     <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B46" s="4">
         <v>6</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>32</v>
@@ -3128,19 +3125,19 @@
         <v>0</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L46"/>
     </row>
     <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B47" s="4">
         <v>7</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>22</v>
@@ -3161,19 +3158,19 @@
         <v>0</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L47"/>
     </row>
     <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B48" s="4">
         <v>9</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>22</v>
@@ -3198,13 +3195,13 @@
     </row>
     <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B49" s="4">
         <v>1</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>12</v>
@@ -3229,7 +3226,7 @@
     </row>
     <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B50" s="4">
         <v>2</v>
@@ -3260,13 +3257,13 @@
     </row>
     <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B51" s="4">
         <v>3</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>48</v>
@@ -3291,13 +3288,13 @@
     </row>
     <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B52" s="4">
         <v>4</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>48</v>
@@ -3322,22 +3319,22 @@
     </row>
     <row r="53" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="B53" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E53" s="4">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="F53" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G53" s="4">
         <v>0</v>
@@ -3346,35 +3343,35 @@
         <v>0</v>
       </c>
       <c r="I53" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="4"/>
       <c r="L53"/>
     </row>
     <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="B54" s="4">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E54" s="4">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="F54" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G54" s="4">
         <v>0</v>
       </c>
       <c r="H54" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="4" t="b">
         <v>0</v>
@@ -3384,19 +3381,19 @@
     </row>
     <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="B55" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E55" s="4">
-        <v>50</v>
+        <v>14</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="F55" s="4">
         <v>0</v>
@@ -3405,7 +3402,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="4" t="b">
         <v>0</v>
@@ -3415,19 +3412,19 @@
     </row>
     <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="B56" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E56" s="4">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="F56" s="4">
         <v>0</v>
@@ -3436,7 +3433,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="4" t="b">
         <v>0</v>
@@ -3446,19 +3443,19 @@
     </row>
     <row r="57" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="B57" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E57" s="4">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="F57" s="4">
         <v>0</v>
@@ -3472,32 +3469,30 @@
       <c r="I57" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J57" s="4" t="s">
-        <v>171</v>
-      </c>
+      <c r="J57" s="4"/>
       <c r="L57"/>
     </row>
     <row r="58" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="B58" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E58" s="4">
-        <v>8</v>
+        <v>14</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="F58" s="4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G58" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H58" s="4" t="b">
         <v>1</v>
@@ -3505,26 +3500,24 @@
       <c r="I58" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J58" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="J58" s="4"/>
       <c r="L58"/>
     </row>
     <row r="59" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B59" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E59" s="4">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="F59" s="4">
         <v>0</v>
@@ -3538,26 +3531,24 @@
       <c r="I59" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J59" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="J59" s="4"/>
       <c r="L59"/>
     </row>
     <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B60" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E60" s="4">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="F60" s="4">
         <v>0</v>
@@ -3571,60 +3562,60 @@
       <c r="I60" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J60" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="J60" s="4"/>
       <c r="L60"/>
     </row>
     <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B61" s="4">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>179</v>
+        <v>32</v>
       </c>
       <c r="E61" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F61" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G61" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J61" s="4"/>
+      <c r="J61" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="L61"/>
     </row>
     <row r="62" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B62" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E62" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F62" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G62" s="4">
         <v>0</v>
@@ -3635,49 +3626,53 @@
       <c r="I62" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J62" s="4"/>
+      <c r="J62" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="L62"/>
     </row>
     <row r="63" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B63" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E63" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F63" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G63" s="4">
         <v>0</v>
       </c>
       <c r="H63" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J63" s="4"/>
+      <c r="J63" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L63"/>
     </row>
     <row r="64" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B64" s="4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>174</v>
+        <v>25</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>12</v>
@@ -3695,31 +3690,29 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>148</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J64" s="4"/>
       <c r="L64"/>
     </row>
     <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="B65" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E65" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F65" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G65" s="4">
         <v>0</v>
@@ -3737,22 +3730,22 @@
     </row>
     <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B66" s="4">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E66" s="4">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F66" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G66" s="4">
         <v>0</v>
@@ -3763,29 +3756,27 @@
       <c r="I66" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J66" s="4" t="s">
-        <v>148</v>
-      </c>
+      <c r="J66" s="4"/>
       <c r="L66"/>
     </row>
     <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B67" s="4">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E67" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F67" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G67" s="4">
         <v>0</v>
@@ -3796,29 +3787,27 @@
       <c r="I67" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J67" s="4" t="s">
-        <v>148</v>
-      </c>
+      <c r="J67" s="4"/>
       <c r="L67"/>
     </row>
     <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B68" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>177</v>
+        <v>38</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E68" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F68" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="4">
         <v>0</v>
@@ -3829,20 +3818,18 @@
       <c r="I68" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J68" s="4" t="s">
-        <v>148</v>
-      </c>
+      <c r="J68" s="4"/>
       <c r="L68"/>
     </row>
     <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="B69" s="4">
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>12</v>
@@ -3867,13 +3854,13 @@
     </row>
     <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="B70" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>44</v>
+        <v>186</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>12</v>
@@ -3898,22 +3885,22 @@
     </row>
     <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="B71" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" s="4" t="s">
-        <v>224</v>
+        <v>41</v>
+      </c>
+      <c r="E71" s="4">
+        <v>1</v>
       </c>
       <c r="F71" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="4">
         <v>0</v>
@@ -3924,24 +3911,26 @@
       <c r="I71" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J71" s="4"/>
+      <c r="J71" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="L71"/>
     </row>
     <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="B72" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E72" s="4" t="s">
-        <v>224</v>
+      <c r="E72" s="4">
+        <v>100</v>
       </c>
       <c r="F72" s="4">
         <v>0</v>
@@ -3960,84 +3949,86 @@
     </row>
     <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="B73" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>224</v>
+        <v>22</v>
+      </c>
+      <c r="E73" s="4">
+        <v>8</v>
       </c>
       <c r="F73" s="4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G73" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H73" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J73" s="4"/>
+      <c r="J73" s="4" t="s">
+        <v>157</v>
+      </c>
       <c r="L73"/>
     </row>
     <row r="74" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="B74" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>224</v>
+        <v>12</v>
+      </c>
+      <c r="E74" s="4">
+        <v>4</v>
       </c>
       <c r="F74" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G74" s="4">
         <v>0</v>
       </c>
       <c r="H74" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="4"/>
       <c r="L74"/>
     </row>
     <row r="75" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="B75" s="4">
         <v>2</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E75" s="4">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="F75" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G75" s="4">
         <v>0</v>
@@ -4053,22 +4044,22 @@
     </row>
     <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="B76" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E76" s="4">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F76" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G76" s="4">
         <v>0</v>
@@ -4084,19 +4075,19 @@
     </row>
     <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B77" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E77" s="4">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="F77" s="4">
         <v>0</v>
@@ -4110,26 +4101,24 @@
       <c r="I77" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J77" s="4" t="s">
-        <v>35</v>
-      </c>
+      <c r="J77" s="4"/>
       <c r="L77"/>
     </row>
     <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B78" s="4">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E78" s="4">
-        <v>7</v>
+        <v>200</v>
       </c>
       <c r="F78" s="4">
         <v>0</v>
@@ -4138,31 +4127,29 @@
         <v>0</v>
       </c>
       <c r="H78" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J78" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="J78" s="4"/>
       <c r="L78"/>
     </row>
     <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B79" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E79" s="4">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="F79" s="4">
         <v>0</v>
@@ -4176,29 +4163,27 @@
       <c r="I79" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J79" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="J79" s="4"/>
       <c r="L79"/>
     </row>
     <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B80" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E80" s="4">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F80" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G80" s="4">
         <v>0</v>
@@ -4207,81 +4192,83 @@
         <v>0</v>
       </c>
       <c r="I80" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="4"/>
       <c r="L80"/>
     </row>
     <row r="81" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B81" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E81" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F81" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" s="4">
         <v>0</v>
       </c>
       <c r="H81" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" s="4" t="b">
         <v>0</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>42</v>
+        <v>170</v>
       </c>
       <c r="L81"/>
     </row>
     <row r="82" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="B82" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E82" s="4">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="F82" s="4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G82" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H82" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J82" s="4"/>
+      <c r="J82" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="L82"/>
     </row>
     <row r="83" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="B83" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>36</v>
@@ -4304,15 +4291,17 @@
       <c r="I83" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J83" s="4"/>
+      <c r="J83" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="L83"/>
     </row>
     <row r="84" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="B84" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>38</v>
@@ -4335,49 +4324,51 @@
       <c r="I84" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J84" s="4"/>
+      <c r="J84" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L84"/>
     </row>
     <row r="85" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="B85" s="4">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>172</v>
+        <v>53</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>12</v>
+        <v>178</v>
       </c>
       <c r="E85" s="4">
+        <v>5</v>
+      </c>
+      <c r="F85" s="4">
         <v>4</v>
       </c>
-      <c r="F85" s="4">
-        <v>10</v>
-      </c>
       <c r="G85" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H85" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="4"/>
       <c r="L85"/>
     </row>
     <row r="86" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="B86" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>187</v>
+        <v>44</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>12</v>
@@ -4402,22 +4393,22 @@
     </row>
     <row r="87" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="B87" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E87" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G87" s="4">
         <v>0</v>
@@ -4428,63 +4419,63 @@
       <c r="I87" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J87" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="J87" s="4"/>
       <c r="L87"/>
     </row>
     <row r="88" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="B88" s="4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E88" s="4">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F88" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G88" s="4">
         <v>0</v>
       </c>
       <c r="H88" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J88" s="4"/>
+      <c r="J88" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="L88"/>
     </row>
     <row r="89" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="B89" s="4">
+        <v>12</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" s="4">
         <v>4</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E89" s="4">
-        <v>8</v>
-      </c>
       <c r="F89" s="4">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G89" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H89" s="4" t="b">
         <v>0</v>
@@ -4493,19 +4484,19 @@
         <v>0</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>158</v>
+        <v>42</v>
       </c>
       <c r="L89"/>
     </row>
     <row r="90" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="B90" s="4">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>12</v>
@@ -4523,20 +4514,22 @@
         <v>0</v>
       </c>
       <c r="I90" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J90" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="L90"/>
     </row>
     <row r="91" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="B91" s="4">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>44</v>
+        <v>177</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>12</v>
@@ -4556,27 +4549,29 @@
       <c r="I91" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J91" s="4"/>
+      <c r="J91" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="L91"/>
     </row>
     <row r="92" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="B92" s="4">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E92" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F92" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G92" s="4">
         <v>0</v>
@@ -4587,7 +4582,9 @@
       <c r="I92" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J92" s="4"/>
+      <c r="J92" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="L92"/>
     </row>
     <row r="93" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4595,25 +4592,25 @@
         <v>43</v>
       </c>
       <c r="B93" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E93" s="4">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="F93" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G93" s="4">
         <v>0</v>
       </c>
       <c r="H93" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" s="4" t="b">
         <v>0</v>
@@ -4626,19 +4623,19 @@
         <v>43</v>
       </c>
       <c r="B94" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="E94" s="4">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="F94" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G94" s="4">
         <v>0</v>
@@ -4654,19 +4651,19 @@
     </row>
     <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B95" s="4">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E95" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F95" s="4">
         <v>0</v>
@@ -4675,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="H95" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" s="4" t="b">
         <v>0</v>
@@ -4685,22 +4682,22 @@
     </row>
     <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B96" s="4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E96" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F96" s="4">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G96" s="4">
         <v>0</v>
@@ -4711,29 +4708,27 @@
       <c r="I96" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J96" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="J96" s="4"/>
       <c r="L96"/>
     </row>
     <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B97" s="4">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E97" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F97" s="4">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G97" s="4">
         <v>0</v>
@@ -4744,29 +4739,27 @@
       <c r="I97" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J97" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="J97" s="4"/>
       <c r="L97"/>
     </row>
     <row r="98" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B98" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="E98" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F98" s="4">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G98" s="4">
         <v>0</v>
@@ -4782,22 +4775,22 @@
     </row>
     <row r="99" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B99" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="E99" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F99" s="4">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G99" s="4">
         <v>0</v>
@@ -4813,28 +4806,28 @@
     </row>
     <row r="100" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B100" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E100" s="4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F100" s="4">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G100" s="4">
         <v>0</v>
       </c>
       <c r="H100" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" s="4" t="b">
         <v>0</v>
@@ -4844,22 +4837,22 @@
     </row>
     <row r="101" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B101" s="4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E101" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F101" s="4">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="G101" s="4">
         <v>0</v>
@@ -4870,29 +4863,27 @@
       <c r="I101" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J101" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="J101" s="4"/>
       <c r="L101"/>
     </row>
     <row r="102" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B102" s="4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>59</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E102" s="4">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F102" s="4">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G102" s="4">
         <v>0</v>
@@ -4908,16 +4899,16 @@
     </row>
     <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B103" s="4">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C103" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D103" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D103" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="E103" s="4">
         <v>8</v>
@@ -4939,16 +4930,16 @@
     </row>
     <row r="104" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B104" s="4">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E104" s="4">
         <v>8</v>
@@ -4970,16 +4961,16 @@
     </row>
     <row r="105" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B105" s="4">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E105" s="4">
         <v>8</v>
@@ -5001,16 +4992,16 @@
     </row>
     <row r="106" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B106" s="4">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E106" s="4">
         <v>8</v>
@@ -5032,53 +5023,55 @@
     </row>
     <row r="107" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B107" s="4">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E107" s="4">
         <v>8</v>
       </c>
       <c r="F107" s="4">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="G107" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H107" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J107" s="4"/>
+      <c r="J107" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="L107"/>
     </row>
     <row r="108" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B108" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E108" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F108" s="4">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G108" s="4">
         <v>0</v>
@@ -5089,27 +5082,29 @@
       <c r="I108" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J108" s="4"/>
+      <c r="J108" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="L108"/>
     </row>
     <row r="109" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B109" s="4">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E109" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F109" s="4">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G109" s="4">
         <v>0</v>
@@ -5120,27 +5115,29 @@
       <c r="I109" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J109" s="4"/>
+      <c r="J109" s="4" t="s">
+        <v>37</v>
+      </c>
       <c r="L109"/>
     </row>
     <row r="110" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B110" s="4">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E110" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F110" s="4">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G110" s="4">
         <v>0</v>
@@ -5151,27 +5148,29 @@
       <c r="I110" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J110" s="4"/>
+      <c r="J110" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="L110"/>
     </row>
     <row r="111" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B111" s="4">
+        <v>1</v>
+      </c>
+      <c r="C111" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B111" s="4">
-        <v>14</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="D111" s="4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E111" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F111" s="4">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G111" s="4">
         <v>0</v>
@@ -5180,35 +5179,35 @@
         <v>0</v>
       </c>
       <c r="I111" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" s="4"/>
       <c r="L111"/>
     </row>
     <row r="112" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B112" s="4">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E112" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F112" s="4">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G112" s="4">
         <v>0</v>
       </c>
       <c r="H112" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" s="4" t="b">
         <v>0</v>
@@ -5218,22 +5217,22 @@
     </row>
     <row r="113" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B113" s="4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="E113" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F113" s="4">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G113" s="4">
         <v>0</v>
@@ -5249,25 +5248,25 @@
     </row>
     <row r="114" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B114" s="4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E114" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F114" s="4">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G114" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H114" s="4" t="b">
         <v>1</v>
@@ -5275,29 +5274,27 @@
       <c r="I114" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J114" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="J114" s="4"/>
       <c r="L114"/>
     </row>
     <row r="115" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="B115" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E115" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F115" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G115" s="4">
         <v>0</v>
@@ -5306,134 +5303,130 @@
         <v>0</v>
       </c>
       <c r="I115" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J115" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J115" s="4"/>
       <c r="L115"/>
     </row>
     <row r="116" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="B116" s="4">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E116" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F116" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G116" s="4">
         <v>0</v>
       </c>
       <c r="H116" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J116" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="J116" s="4"/>
       <c r="L116"/>
     </row>
     <row r="117" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="B117" s="4">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E117" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F117" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G117" s="4">
         <v>0</v>
       </c>
       <c r="H117" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J117" s="4" t="s">
-        <v>39</v>
-      </c>
+      <c r="J117" s="4"/>
       <c r="L117"/>
     </row>
     <row r="118" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="B118" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E118" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F118" s="4">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G118" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H118" s="4" t="b">
         <v>0</v>
       </c>
       <c r="I118" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J118" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="L118"/>
     </row>
     <row r="119" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="B119" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E119" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F119" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G119" s="4">
         <v>0</v>
       </c>
       <c r="H119" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="4" t="b">
         <v>0</v>
@@ -5443,19 +5436,19 @@
     </row>
     <row r="120" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="B120" s="4">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E120" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F120" s="4">
         <v>0</v>
@@ -5474,13 +5467,13 @@
     </row>
     <row r="121" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="B121" s="4">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>12</v>
@@ -5495,23 +5488,23 @@
         <v>0</v>
       </c>
       <c r="H121" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="4"/>
       <c r="L121"/>
     </row>
     <row r="122" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="B122" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>12</v>
@@ -5529,29 +5522,29 @@
         <v>0</v>
       </c>
       <c r="I122" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" s="4"/>
       <c r="L122"/>
     </row>
     <row r="123" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="B123" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>192</v>
+        <v>26</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E123" s="4">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="F123" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G123" s="4">
         <v>0</v>
@@ -5567,22 +5560,22 @@
     </row>
     <row r="124" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="B124" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E124" s="4">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F124" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G124" s="4">
         <v>0</v>
@@ -5598,83 +5591,83 @@
     </row>
     <row r="125" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B125" s="4">
         <v>4</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E125" s="4">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F125" s="4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G125" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H125" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J125" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="J125" s="4"/>
       <c r="L125"/>
     </row>
     <row r="126" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B126" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>36</v>
+        <v>165</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E126" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F126" s="4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G126" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H126" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I126" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J126" s="4"/>
+      <c r="J126" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="L126"/>
     </row>
     <row r="127" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B127" s="4">
         <v>6</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E127" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F127" s="4">
         <v>0</v>
@@ -5683,7 +5676,7 @@
         <v>0</v>
       </c>
       <c r="H127" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" s="4" t="b">
         <v>0</v>
@@ -5693,44 +5686,44 @@
     </row>
     <row r="128" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B128" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>192</v>
+        <v>38</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E128" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F128" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G128" s="4">
         <v>0</v>
       </c>
       <c r="H128" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" s="4"/>
       <c r="L128"/>
     </row>
     <row r="129" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B129" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>44</v>
+        <v>192</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>12</v>
@@ -5748,35 +5741,35 @@
         <v>0</v>
       </c>
       <c r="I129" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" s="4"/>
       <c r="L129"/>
     </row>
     <row r="130" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B130" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E130" s="4">
-        <v>200</v>
+        <v>4</v>
       </c>
       <c r="F130" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G130" s="4">
         <v>0</v>
       </c>
       <c r="H130" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" s="4" t="b">
         <v>0</v>
@@ -5786,22 +5779,22 @@
     </row>
     <row r="131" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B131" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E131" s="4">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F131" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G131" s="4">
         <v>0</v>
@@ -5817,25 +5810,25 @@
     </row>
     <row r="132" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B132" s="4">
         <v>4</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E132" s="4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F132" s="4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G132" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H132" s="4" t="b">
         <v>1</v>
@@ -5843,97 +5836,97 @@
       <c r="I132" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J132" s="4"/>
+      <c r="J132" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="L132"/>
     </row>
     <row r="133" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B133" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>166</v>
+        <v>51</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="E133" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F133" s="4">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G133" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H133" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J133" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="J133" s="4"/>
       <c r="L133"/>
     </row>
     <row r="134" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B134" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E134" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F134" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G134" s="4">
         <v>0</v>
       </c>
       <c r="H134" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J134" s="4"/>
       <c r="L134"/>
     </row>
     <row r="135" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B135" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E135" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F135" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G135" s="4">
         <v>0</v>
       </c>
       <c r="H135" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I135" s="4" t="b">
         <v>0</v>
@@ -5943,59 +5936,59 @@
     </row>
     <row r="136" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="B136" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E136" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F136" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G136" s="4">
         <v>0</v>
       </c>
       <c r="H136" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I136" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J136" s="4"/>
       <c r="L136"/>
     </row>
     <row r="137" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="B137" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E137" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F137" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G137" s="4">
         <v>0</v>
       </c>
       <c r="H137" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" s="4" t="b">
         <v>0</v>
@@ -6005,22 +5998,22 @@
     </row>
     <row r="138" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="B138" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E138" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F138" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G138" s="4">
         <v>0</v>
@@ -6036,25 +6029,25 @@
     </row>
     <row r="139" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="B139" s="4">
+        <v>1</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E139" s="4">
         <v>4</v>
       </c>
-      <c r="C139" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D139" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E139" s="4">
-        <v>8</v>
-      </c>
       <c r="F139" s="4">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G139" s="4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H139" s="4" t="b">
         <v>1</v>
@@ -6062,35 +6055,33 @@
       <c r="I139" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J139" s="4" t="s">
-        <v>23</v>
-      </c>
+      <c r="J139" s="4"/>
       <c r="L139"/>
     </row>
     <row r="140" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="B140" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>179</v>
+        <v>12</v>
       </c>
       <c r="E140" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F140" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G140" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H140" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" s="4" t="b">
         <v>0</v>
@@ -6098,253 +6089,36 @@
       <c r="J140" s="4"/>
       <c r="L140"/>
     </row>
-    <row r="141" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B141" s="4">
-        <v>1</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D141" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E141" s="4">
-        <v>4</v>
-      </c>
-      <c r="F141" s="4">
-        <v>10</v>
-      </c>
-      <c r="G141" s="4">
-        <v>0</v>
-      </c>
-      <c r="H141" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I141" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J141" s="4"/>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A141" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B141" s="6">
+        <v>3</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F141" s="6">
+        <v>0</v>
+      </c>
+      <c r="G141" s="6">
+        <v>0</v>
+      </c>
+      <c r="H141" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I141" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J141" s="6"/>
       <c r="L141"/>
-    </row>
-    <row r="142" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B142" s="4">
-        <v>2</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E142" s="4">
-        <v>4</v>
-      </c>
-      <c r="F142" s="4">
-        <v>10</v>
-      </c>
-      <c r="G142" s="4">
-        <v>0</v>
-      </c>
-      <c r="H142" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I142" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J142" s="4"/>
-      <c r="L142"/>
-    </row>
-    <row r="143" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B143" s="4">
-        <v>2</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E143" s="4">
-        <v>20</v>
-      </c>
-      <c r="F143" s="4">
-        <v>0</v>
-      </c>
-      <c r="G143" s="4">
-        <v>0</v>
-      </c>
-      <c r="H143" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I143" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J143" s="4"/>
-      <c r="L143"/>
-    </row>
-    <row r="144" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B144" s="4">
-        <v>4</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D144" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E144" s="4">
-        <v>7</v>
-      </c>
-      <c r="F144" s="4">
-        <v>0</v>
-      </c>
-      <c r="G144" s="4">
-        <v>0</v>
-      </c>
-      <c r="H144" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I144" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J144" s="4"/>
-      <c r="L144"/>
-    </row>
-    <row r="145" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A145" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B145" s="4">
-        <v>5</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D145" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E145" s="4">
-        <v>6</v>
-      </c>
-      <c r="F145" s="4">
-        <v>0</v>
-      </c>
-      <c r="G145" s="4">
-        <v>0</v>
-      </c>
-      <c r="H145" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I145" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J145" s="4"/>
-      <c r="L145"/>
-    </row>
-    <row r="146" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B146" s="4">
-        <v>1</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E146" s="4">
-        <v>4</v>
-      </c>
-      <c r="F146" s="4">
-        <v>10</v>
-      </c>
-      <c r="G146" s="4">
-        <v>0</v>
-      </c>
-      <c r="H146" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I146" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J146" s="4"/>
-      <c r="L146"/>
-    </row>
-    <row r="147" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B147" s="4">
-        <v>6</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E147" s="4">
-        <v>4</v>
-      </c>
-      <c r="F147" s="4">
-        <v>10</v>
-      </c>
-      <c r="G147" s="4">
-        <v>0</v>
-      </c>
-      <c r="H147" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I147" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J147" s="4"/>
-      <c r="L147"/>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A148" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B148" s="6">
-        <v>3</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="F148" s="6">
-        <v>0</v>
-      </c>
-      <c r="G148" s="6">
-        <v>0</v>
-      </c>
-      <c r="H148" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I148" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="J148" s="6"/>
-      <c r="L148"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6371,65 +6145,65 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -6437,10 +6211,10 @@
         <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -6448,131 +6222,131 @@
         <v>24</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -6580,10 +6354,10 @@
         <v>30</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -6591,10 +6365,10 @@
         <v>30</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -6602,10 +6376,10 @@
         <v>30</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -6613,32 +6387,32 @@
         <v>30</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="C24" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -6646,10 +6420,10 @@
         <v>43</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -6657,10 +6431,10 @@
         <v>43</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -6668,98 +6442,98 @@
         <v>43</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="C36" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -6785,30 +6559,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" s="3" t="b">
         <v>0</v>
@@ -6834,33 +6608,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>44</v>
@@ -6868,24 +6642,24 @@
     </row>
     <row r="3" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>16</v>
@@ -6894,15 +6668,15 @@
         <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>16</v>
@@ -6919,7 +6693,7 @@
     </row>
     <row r="6" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>16</v>
@@ -6936,7 +6710,7 @@
     </row>
     <row r="7" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>24</v>
@@ -6953,16 +6727,16 @@
     </row>
     <row r="8" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>44</v>
@@ -6970,27 +6744,27 @@
     </row>
     <row r="9" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>44</v>
@@ -7004,33 +6778,33 @@
     </row>
     <row r="11" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>44</v>
@@ -7038,27 +6812,27 @@
     </row>
     <row r="13" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>44</v>
@@ -7072,50 +6846,50 @@
     </row>
     <row r="15" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>44</v>
@@ -7123,16 +6897,16 @@
     </row>
     <row r="18" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>44</v>
@@ -7140,16 +6914,16 @@
     </row>
     <row r="19" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>44</v>
@@ -7157,19 +6931,19 @@
     </row>
     <row r="20" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -7193,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7201,46 +6975,46 @@
     </row>
     <row r="2" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -7248,7 +7022,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>11</v>
@@ -7256,13 +7030,13 @@
     </row>
     <row r="7" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -7270,7 +7044,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>17</v>
@@ -7281,7 +7055,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>19</v>
@@ -7289,21 +7063,21 @@
     </row>
     <row r="10" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>44</v>
@@ -7311,13 +7085,13 @@
     </row>
     <row r="12" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -7325,7 +7099,7 @@
         <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>31</v>
@@ -7333,24 +7107,24 @@
     </row>
     <row r="14" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
@@ -7358,7 +7132,7 @@
         <v>43</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>44</v>
@@ -7366,21 +7140,21 @@
     </row>
     <row r="17" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>18</v>
@@ -7388,32 +7162,32 @@
     </row>
     <row r="19" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>18</v>
